--- a/scrutinise-web/public/central-question-upload-template.xlsx
+++ b/scrutinise-web/public/central-question-upload-template.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="89">
   <si>
     <t>Scrutinise Central — bulk question upload template</t>
   </si>
@@ -246,76 +246,49 @@
     <t>Our local branch is a mature political movement fully realigned from the Uniparty</t>
   </si>
   <si>
-    <t>Attorney General’s Office</t>
-  </si>
-  <si>
-    <t>Cabinet Office</t>
-  </si>
-  <si>
-    <t>Department for Business and Trade</t>
-  </si>
-  <si>
-    <t>Department for Culture, Media and Sport</t>
-  </si>
-  <si>
-    <t>Department for Education</t>
-  </si>
-  <si>
-    <t>Department for Energy Security and Net Zero</t>
-  </si>
-  <si>
-    <t>Department for Environment, Food and Rural Affairs</t>
-  </si>
-  <si>
-    <t>Department for Science, Innovation and Technology</t>
-  </si>
-  <si>
-    <t>Department for Transport</t>
-  </si>
-  <si>
-    <t>Department for Work and Pensions</t>
-  </si>
-  <si>
-    <t>Department of Health and Social Care</t>
-  </si>
-  <si>
-    <t>Foreign, Commonwealth and Development Office</t>
-  </si>
-  <si>
-    <t>HM Treasury</t>
-  </si>
-  <si>
-    <t>Home Office</t>
-  </si>
-  <si>
-    <t>Ministry of Defence</t>
-  </si>
-  <si>
-    <t>Ministry of Housing, Communities and Local Government</t>
-  </si>
-  <si>
-    <t>Ministry of Justice</t>
-  </si>
-  <si>
-    <t>Northern Ireland Office</t>
-  </si>
-  <si>
-    <t>Office of the Advocate General for Scotland</t>
-  </si>
-  <si>
-    <t>Office of the Leader of the House of Commons</t>
-  </si>
-  <si>
-    <t>Office of the Leader of the House of Lords</t>
-  </si>
-  <si>
-    <t>Scotland Office</t>
-  </si>
-  <si>
-    <t>UK Export Finance</t>
-  </si>
-  <si>
-    <t>Wales Office</t>
+    <t>Immigration &amp; asylum</t>
+  </si>
+  <si>
+    <t>Crime, justice &amp; policing</t>
+  </si>
+  <si>
+    <t>Health &amp; care</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Transport &amp; roads</t>
+  </si>
+  <si>
+    <t>Energy &amp; net zero</t>
+  </si>
+  <si>
+    <t>Environment, farming &amp; rural</t>
+  </si>
+  <si>
+    <t>Economy &amp; tax</t>
+  </si>
+  <si>
+    <t>Welfare &amp; pensions</t>
+  </si>
+  <si>
+    <t>Business &amp; jobs</t>
+  </si>
+  <si>
+    <t>Culture, media &amp; sport</t>
+  </si>
+  <si>
+    <t>Science, technology &amp; digital</t>
+  </si>
+  <si>
+    <t>Defence &amp; foreign affairs</t>
+  </si>
+  <si>
+    <t>Constitution, devolution &amp; elections</t>
+  </si>
+  <si>
+    <t>Social &amp; moral issues</t>
   </si>
 </sst>
 </file>
@@ -2825,7 +2798,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="26" customWidth="1"/>
@@ -2851,7 +2824,7 @@
         <v>55</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2862,7 +2835,7 @@
         <v>55</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2873,7 +2846,7 @@
         <v>55</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2884,7 +2857,7 @@
         <v>55</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2895,7 +2868,7 @@
         <v>55</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2906,7 +2879,7 @@
         <v>64</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2917,7 +2890,7 @@
         <v>64</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2928,146 +2901,81 @@
         <v>64</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="C10" s="9" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="C11" s="9" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="C12" s="9" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="C13" s="9" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="C14" s="9" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="C15" s="9" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="C16" s="9" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="C17" s="9" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="C18" s="9" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="C19" s="9" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="C20" s="9" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="C21" s="9" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="C22" s="9" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="C23" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="C24" s="9" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="C25" s="9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="C26" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="C27" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="C28" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="C29" s="9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="C30" s="9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="C31" s="9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="C32" s="9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="C33" s="9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="C34" s="9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="C35" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="C36" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="10" t="s">
+      <c r="A25" s="10" t="s">
         <v>71</v>
       </c>
     </row>
